--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.76.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.76.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.76" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.76" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.76.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.76.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0076.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0076.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.76.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.76.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.76" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.76" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="51" customWidth="1" min="14" max="14"/>
-    <col width="49" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -607,18 +607,18 @@
           <t>L24: line starts with digit/letter garbage token | suspicious token(s): 1exer (letter/digit mix) :: 1exer-</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of a traversing note: or â€”</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of a traversing note : orâ€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]e</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]e</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L4: symbol-only separator/garbage line :: , 835:</t>
@@ -626,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L6: symbol-only separator/garbage line :: ,835.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]e</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -657,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -678,16 +678,8 @@
           <t>L27: line starts with digit/letter garbage token | suspicious token(s): 6been (letter/digit mix) | candidate OCR token mismatch vs other OCR: "been" vs "6been" :: 6been</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: after the date of the order for leave to amend: or â€”</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: after the date of the order for leave to amend: orâ€” amend.</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -697,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L20: isolated marker/symbol line :: &gt;</t>
+          <t>L6: symbol-only separator/garbage line :: ,835.</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -748,7 +740,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: i</t>
+          <t>L20: isolated marker/symbol line :: &gt;</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,12 +762,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -793,7 +785,11 @@
           <t>L38: isolated marker/symbol line :: 8</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L73: isolated marker/symbol line :: i</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -981,12 +977,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1025,7 +1021,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1064,7 +1060,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
